--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555949611</v>
+        <v>46157.93114445432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114445432</v>
+        <v>46157.93138024529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93138024529</v>
+        <v>46157.93385053481</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93385053481</v>
+        <v>46157.93696570861</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696570861</v>
+        <v>46158.28205454884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205454884</v>
+        <v>46158.29653465767</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653465767</v>
+        <v>46158.2980871834</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980871834</v>
+        <v>46158.33371354535</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371354535</v>
+        <v>46158.37222806265</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222806265</v>
+        <v>46158.37276116981</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
